--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -321,16 +321,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -456,7 +456,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -818,61 +818,58 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:endoscopy</t>
-  </si>
-  <si>
-    <t>endoscopy</t>
+    <t>DiagnosticReport.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
   </si>
   <si>
     <t>診断レポートの分野を表すコード。【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポートを作成した臨床分野、部門、または診断サービス（心臓病学、生化学、血液学、放射線医学など）を分類するコード</t>
-  </si>
-  <si>
     <t>JP_DiagnosticReportCategory_VSの中から「LP7796-8」（Endoscopy（内視鏡））を指定する。</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:endoscopy.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.system</t>
+    <t>DiagnosticReport.category:first.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.system</t>
   </si>
   <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:endoscopy.coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.code</t>
+    <t>DiagnosticReport.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.code</t>
   </si>
   <si>
     <t>LP7796-8</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:endoscopy.coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.text</t>
+    <t>DiagnosticReport.category:first.coding.display</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.text</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -1133,11 +1130,14 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Endoscopy)
 </t>
   </si>
   <si>
-    <t>この診断レポートの一部となるObservationに関する情報。</t>
+    <t>この診断レポートの一部となる内視鏡検査、治療による観察結果（診断、所見など）の情報。【詳細参照】</t>
+  </si>
+  <si>
+    <t>この診断レポートの一部となる内視鏡検査、治療による観察結果（診断、所見など）の情報。詳細はJP_Observation_Endoscopyの実装ガイドを参照</t>
   </si>
   <si>
     <t>Observationsは階層構造を持てる。</t>
@@ -1239,7 +1239,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Media_Endoscopy)
 </t>
   </si>
   <si>
@@ -1633,7 +1633,7 @@
   <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.33984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2957,7 +2957,7 @@
         <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
@@ -4576,10 +4576,10 @@
         <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>192</v>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>198</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>203</v>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>212</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>213</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>214</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5340,7 +5340,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>221</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>228</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>234</v>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>240</v>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>249</v>
@@ -5914,14 +5914,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5943,13 +5943,13 @@
         <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5975,11 +5975,11 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5997,7 +5997,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6012,28 +6012,28 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6052,19 +6052,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6113,7 +6113,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6128,28 +6128,28 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6168,19 +6168,19 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6229,7 +6229,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6244,28 +6244,28 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6284,19 +6284,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6345,7 +6345,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6360,28 +6360,28 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6400,19 +6400,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6461,7 +6461,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6479,25 +6479,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6516,19 +6516,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6577,7 +6577,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6592,28 +6592,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6632,19 +6632,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6693,7 +6693,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6708,24 +6708,24 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6748,19 +6748,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6809,7 +6809,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6827,10 +6827,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6838,14 +6838,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6855,7 +6855,7 @@
         <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
@@ -6864,10 +6864,10 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>358</v>
@@ -6925,7 +6925,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7561,7 +7561,7 @@
         <v>386</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>387</v>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -277,7 +277,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -4561,7 +4561,7 @@
         <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -1633,17 +1633,17 @@
   <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.01171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.01953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="207.65625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="178.02734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1652,26 +1652,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="55.07421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.30078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.26953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="147.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="104.53515625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -375,7 +375,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -600,7 +600,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1104,7 +1104,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
